--- a/salida/simulacion.xlsx
+++ b/salida/simulacion.xlsx
@@ -550,22 +550,22 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.15</v>
+        <v>0.52</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="H2" t="n">
-        <v>239.55</v>
+        <v>153.24</v>
       </c>
       <c r="I2" t="n">
-        <v>239.55</v>
+        <v>153.24</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -579,16 +579,16 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>esperando_ascenso</t>
+          <t>esperando_descenso</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>15</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -606,24 +606,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fin_ascenso</t>
+          <t>fin_descenso</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>239.55</v>
+        <v>153.24</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -637,17 +637,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>esperando</t>
+          <t>esperando_ascenso</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>10</v>
-      </c>
+      <c r="S3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
         <v>0</v>
       </c>
@@ -655,7 +655,7 @@
         <v>5</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -664,102 +664,94 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fin_espera</t>
+          <t>fin_ascenso</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>239.55</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>324</v>
-      </c>
-      <c r="L4" t="n">
-        <v>334</v>
-      </c>
+        <v>153.24</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>baja</t>
+          <t>sube</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>en_movimiento</t>
+          <t>esperando</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>35</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
       <c r="V4" t="n">
         <v>5</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>llegada_pasajero</t>
+          <t>fin_espera</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>239.55</v>
+        <v>35</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H5" t="n">
-        <v>38.35</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>277.9</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+        <v>153.24</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K5" t="n">
+        <v>392.4</v>
+      </c>
       <c r="L5" t="n">
-        <v>334</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
+        <v>427.4</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>baja</t>
@@ -778,13 +770,13 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -794,32 +786,32 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>277.9</v>
+        <v>153.24</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.38</v>
+        <v>0.92</v>
       </c>
       <c r="H6" t="n">
-        <v>143.41</v>
+        <v>757.71</v>
       </c>
       <c r="I6" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -844,13 +836,13 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -860,29 +852,29 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.17</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -897,24 +889,24 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>349</v>
+        <v>432.4</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="V7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -924,29 +916,29 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C8" t="n">
-        <v>0.19</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -961,24 +953,24 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>339</v>
+        <v>442.4</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -988,29 +980,29 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C9" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.13</v>
+        <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1021,28 +1013,28 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>esperando_ascenso</t>
+          <t>esperando_descenso</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>359</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>437.4</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -1052,29 +1044,29 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6</v>
+        <v>0.41</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1092,21 +1084,21 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>354</v>
+        <v>437.4</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -1116,29 +1108,29 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C11" t="n">
-        <v>0.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.68</v>
+        <v>0.38</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1153,24 +1145,24 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>354</v>
+        <v>437.4</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -1180,16 +1172,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C12" t="n">
-        <v>0.57</v>
+        <v>0.92</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.99</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1197,12 +1189,12 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1217,24 +1209,24 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>349</v>
+        <v>442.4</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -1244,29 +1236,29 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C13" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1284,21 +1276,21 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>344</v>
+        <v>442.4</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -1308,29 +1300,29 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C14" t="n">
-        <v>0.78</v>
+        <v>0.49</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0.89</v>
+        <v>0.37</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -1345,24 +1337,24 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>359</v>
+        <v>432.4</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -1372,25 +1364,29 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C15" t="n">
-        <v>0.12</v>
+        <v>0.93</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -1401,28 +1397,28 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>esperando_ascenso</t>
+          <t>esperando_descenso</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>344</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>432.4</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -1432,29 +1428,29 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C16" t="n">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6</v>
+        <v>0.34</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -1469,24 +1465,24 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>344</v>
+        <v>432.4</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1496,29 +1492,29 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C17" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>0.31</v>
+        <v>0.6</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>421.3</v>
+        <v>910.95</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -1536,21 +1532,21 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>344</v>
+        <v>447.4</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1560,29 +1556,29 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>334</v>
+        <v>427.4</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>421.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="K18" t="n">
-        <v>223.2</v>
-      </c>
+        <v>910.95</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>557.2</v>
+        <v>427.4</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -1593,88 +1589,92 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>en_movimiento</t>
+          <t>esperando_descenso</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>432.4</v>
+      </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>427.4</v>
+      </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>llegada_pasajero</t>
+          <t>llegada_ascensor</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>421.3</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>427.4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.32</v>
+      </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>361.19</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>782.49</v>
+        <v>910.95</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>557.2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N19" t="inlineStr">
+        <v>427.4</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>en_movimiento</t>
+          <t>esperando_descenso</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
-      </c>
-      <c r="R19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>432.4</v>
+      </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>427.4</v>
+      </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -1684,29 +1684,29 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>557.2</v>
+        <v>427.4</v>
       </c>
       <c r="C20" t="n">
-        <v>0.66</v>
+        <v>0.43</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.31</v>
+        <v>0.8</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>782.49</v>
+        <v>910.95</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>557.2</v>
+        <v>427.4</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -1721,24 +1721,24 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>562.2</v>
+        <v>442.4</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
-        <v>557.2</v>
+        <v>427.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
@@ -1748,33 +1748,29 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>557.2</v>
+        <v>427.4</v>
       </c>
       <c r="C21" t="n">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01</v>
+        <v>0.37</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>782.49</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K21" t="n">
-        <v>198</v>
-      </c>
+        <v>910.95</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>755.2</v>
+        <v>427.4</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -1785,24 +1781,28 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>en_movimiento</t>
+          <t>esperando_descenso</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>437.4</v>
+      </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>427.4</v>
+      </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/salida/simulacion.xlsx
+++ b/salida/simulacion.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,13 +26,77 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6B8AF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E0E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4C6E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEFEF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,8 +111,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,124 +516,150 @@
   </sheetPr>
   <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>EVENTO</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>RELOJ</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>RELOJ (seg)</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>RND_LLEGADA_ASCENSOR</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>LLEGADA_ASCENSOR</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>PROXIMA_LLEGADA_ASCENSOR</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>RND_H</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>RND_P</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>RND_LLEGADA_PASAJERO</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>LLEGADA_PASAJERO</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>PROXIMA_LLEGADA_PASAJERO</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>RND_LLEGADA_ASCENSOR</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>LLEGADA_ASCENSOR</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>PROXIMA_LLEGADA_ASCENSOR</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>RND_DIRECCION_PASAJERO</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>DIRECCION_PASAJERO</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>DIRECCION_ASCENSOR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>ESTADO_ASCENSOR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>ESPACIO_DISPONIBLE</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>INICIO_DETENCION</t>
+        </is>
+      </c>
+      <c r="S1" s="8" t="inlineStr">
         <is>
           <t>FIN_DESCENSO</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>FIN_ASCENSO</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" s="10" t="inlineStr">
         <is>
           <t>FIN_ESPERA</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>INICIO_DETENCION</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="11" t="inlineStr">
         <is>
           <t>COLA_BAJA</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="11" t="inlineStr">
         <is>
           <t>COLA_SUBE</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="12" t="inlineStr">
         <is>
           <t>ACUMULADOR_PERMANENCIA</t>
         </is>
@@ -549,27 +675,27 @@
         <v>0</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>153.24</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>153.24</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K2" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>98.55</v>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
@@ -586,13 +712,13 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>15</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>20</v>
+      </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
         <v>5</v>
       </c>
@@ -610,24 +736,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>153.24</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>98.55</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
@@ -641,16 +767,16 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>35</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
         <v>5</v>
       </c>
@@ -668,24 +794,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>153.24</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>98.55</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
@@ -699,15 +825,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>35</v>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V4" t="n">
         <v>5</v>
@@ -726,29 +852,29 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.68</v>
+      </c>
       <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>424.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>464.8</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>153.24</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="K5" t="n">
-        <v>392.4</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>427.4</v>
+        <v>98.55</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -776,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -786,32 +912,32 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>153.24</v>
+        <v>98.55</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>464.8</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H6" t="n">
-        <v>757.71</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>910.95</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K6" t="n">
+        <v>514.4299999999999</v>
+      </c>
       <c r="L6" t="n">
-        <v>427.4</v>
+        <v>612.97</v>
       </c>
       <c r="M6" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -842,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -852,29 +978,29 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
+        <v>464.8</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>464.8</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.79</v>
+      </c>
       <c r="I7" t="n">
-        <v>910.95</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>427.4</v>
+        <v>612.97</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -889,16 +1015,16 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>432.4</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
+        <v>464.8</v>
+      </c>
+      <c r="S7" t="n">
+        <v>479.8</v>
+      </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
         <v>6</v>
       </c>
@@ -906,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -916,29 +1042,29 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D8" t="n">
+        <v>464.8</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>464.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G8" t="n">
         <v>4</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0.29</v>
+      </c>
       <c r="I8" t="n">
-        <v>910.95</v>
+        <v>1</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>427.4</v>
+        <v>612.97</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -956,13 +1082,13 @@
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>442.4</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
+        <v>464.8</v>
+      </c>
+      <c r="S8" t="n">
+        <v>469.8</v>
+      </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
         <v>6</v>
       </c>
@@ -970,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -980,29 +1106,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
+        <v>464.8</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>0.9</v>
+        <v>464.8</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>0.06</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
-        <v>910.95</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>427.4</v>
+        <v>612.97</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1013,28 +1135,28 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>esperando_descenso</t>
+          <t>esperando_ascenso</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>437.4</v>
+        <v>464.8</v>
       </c>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="T9" t="n">
+        <v>494.8</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -1044,29 +1166,29 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6</v>
-      </c>
+        <v>464.8</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>0.41</v>
+        <v>464.8</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+        <v>0.26</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I10" t="n">
-        <v>910.95</v>
+        <v>1</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>427.4</v>
+        <v>612.97</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1081,24 +1203,24 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>437.4</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
+        <v>464.8</v>
+      </c>
+      <c r="S10" t="n">
+        <v>469.8</v>
+      </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -1108,29 +1230,29 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
+        <v>464.8</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>0.38</v>
+        <v>464.8</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+        <v>0.22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.92</v>
+      </c>
       <c r="I11" t="n">
-        <v>910.95</v>
+        <v>1</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>427.4</v>
+        <v>612.97</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1145,24 +1267,24 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>437.4</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
+        <v>464.8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>469.8</v>
+      </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -1172,29 +1294,29 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="D12" t="n">
+        <v>464.8</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>464.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G12" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>0.91</v>
+      </c>
       <c r="I12" t="n">
-        <v>910.95</v>
+        <v>6</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>427.4</v>
+        <v>612.97</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1212,21 +1334,21 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>442.4</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
+        <v>464.8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>494.8</v>
+      </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -1236,29 +1358,29 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
-      </c>
+        <v>464.8</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>464.8</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+        <v>0.31</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.74</v>
+      </c>
       <c r="I13" t="n">
-        <v>910.95</v>
+        <v>2</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>427.4</v>
+        <v>612.97</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1273,24 +1395,24 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>442.4</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
+        <v>464.8</v>
+      </c>
+      <c r="S13" t="n">
+        <v>474.8</v>
+      </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -1300,29 +1422,33 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>427.4</v>
+        <v>464.8</v>
       </c>
       <c r="C14" t="n">
         <v>0.49</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>356.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0.37</v>
+        <v>821.2</v>
       </c>
       <c r="F14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>0.01</v>
+      </c>
       <c r="I14" t="n">
-        <v>910.95</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>427.4</v>
+        <v>612.97</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -1333,63 +1459,65 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>esperando_descenso</t>
+          <t>en_movimiento</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>432.4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>llegada_ascensor</t>
+          <t>llegada_pasajero</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6</v>
-      </c>
+        <v>612.97</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F15" t="n">
+        <v>821.2</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>910.95</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K15" t="n">
+        <v>392.79</v>
+      </c>
       <c r="L15" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+        <v>1005.76</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>baja</t>
@@ -1397,28 +1525,24 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>esperando_descenso</t>
+          <t>en_movimiento</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>432.4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -1428,29 +1552,29 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
+        <v>821.2</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>0.34</v>
+        <v>821.2</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.93</v>
+      </c>
       <c r="I16" t="n">
-        <v>910.95</v>
+        <v>5</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>427.4</v>
+        <v>1005.76</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -1465,24 +1589,24 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>432.4</v>
-      </c>
-      <c r="S16" t="inlineStr"/>
+        <v>821.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>846.2</v>
+      </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
@@ -1492,29 +1616,29 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6</v>
-      </c>
+        <v>821.2</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>0.6</v>
+        <v>821.2</v>
       </c>
       <c r="F17" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I17" t="n">
         <v>4</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
-        <v>910.95</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>427.4</v>
+        <v>1005.76</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -1529,24 +1653,24 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>447.4</v>
-      </c>
-      <c r="S17" t="inlineStr"/>
+        <v>821.2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>841.2</v>
+      </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -1556,29 +1680,29 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
+        <v>821.2</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>0.35</v>
+        <v>821.2</v>
       </c>
       <c r="F18" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I18" t="n">
         <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>910.95</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>427.4</v>
+        <v>1005.76</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -1593,24 +1717,24 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>432.4</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
+        <v>821.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>826.2</v>
+      </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1620,29 +1744,29 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
+        <v>821.2</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>0.45</v>
+        <v>821.2</v>
       </c>
       <c r="F19" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G19" t="n">
         <v>1</v>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0.75</v>
+      </c>
       <c r="I19" t="n">
-        <v>910.95</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>427.4</v>
+        <v>1005.76</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -1657,24 +1781,24 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>432.4</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
+        <v>821.2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>826.2</v>
+      </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -1684,29 +1808,29 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
+        <v>821.2</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>0.8</v>
+        <v>821.2</v>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+        <v>0.79</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.32</v>
+      </c>
       <c r="I20" t="n">
-        <v>910.95</v>
+        <v>1</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>427.4</v>
+        <v>1005.76</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -1721,24 +1845,24 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>442.4</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
+        <v>821.2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>826.2</v>
+      </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -1748,29 +1872,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>427.4</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D21" t="n">
-        <v>5</v>
-      </c>
+        <v>821.2</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>0.37</v>
+        <v>821.2</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+        <v>0.06</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="n">
-        <v>910.95</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>427.4</v>
+        <v>1005.76</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -1781,28 +1901,28 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>esperando_descenso</t>
+          <t>esperando_ascenso</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>437.4</v>
+        <v>821.2</v>
       </c>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="n">
-        <v>427.4</v>
-      </c>
+      <c r="T21" t="n">
+        <v>826.2</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/salida/simulacion.xlsx
+++ b/salida/simulacion.xlsx
@@ -682,19 +682,19 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="K2" t="n">
-        <v>98.55</v>
+        <v>107</v>
       </c>
       <c r="L2" t="n">
-        <v>98.55</v>
+        <v>107</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -747,12 +747,12 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>98.55</v>
+        <v>107</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -767,14 +767,14 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -805,12 +805,12 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>98.55</v>
+        <v>107</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V4" t="n">
         <v>5</v>
@@ -852,16 +852,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
-        <v>0.68</v>
+        <v>0.41</v>
       </c>
       <c r="D5" t="n">
-        <v>424.8</v>
+        <v>327.6</v>
       </c>
       <c r="E5" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
@@ -869,12 +869,12 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>98.55</v>
+        <v>107</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -912,12 +912,12 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>98.55</v>
+        <v>107</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
@@ -925,19 +925,19 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="K6" t="n">
-        <v>514.4299999999999</v>
+        <v>371.36</v>
       </c>
       <c r="L6" t="n">
-        <v>612.97</v>
+        <v>478.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0.36</v>
+        <v>0.26</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -978,29 +978,29 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>612.97</v>
+        <v>478.36</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="S7" t="n">
-        <v>479.8</v>
+        <v>377.6</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1064,7 +1064,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>612.97</v>
+        <v>478.36</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="S8" t="n">
-        <v>469.8</v>
+        <v>377.6</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
@@ -1106,25 +1106,29 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06</v>
+        <v>0.72</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>612.97</v>
+        <v>478.36</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1135,28 +1139,28 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>esperando_ascenso</t>
+          <t>esperando_descenso</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>464.8</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="n">
-        <v>494.8</v>
-      </c>
+        <v>372.6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>397.6</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -1166,29 +1170,29 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="F10" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>612.97</v>
+        <v>478.36</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1203,24 +1207,24 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="S10" t="n">
-        <v>469.8</v>
+        <v>382.6</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -1230,29 +1234,29 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>612.97</v>
+        <v>478.36</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1267,24 +1271,24 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="S11" t="n">
-        <v>469.8</v>
+        <v>382.6</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -1294,29 +1298,29 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>612.97</v>
+        <v>478.36</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1334,21 +1338,21 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="S12" t="n">
-        <v>494.8</v>
+        <v>377.6</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -1358,21 +1362,21 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.31</v>
+        <v>0.75</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.74</v>
+        <v>0.46</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
@@ -1380,7 +1384,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>612.97</v>
+        <v>478.36</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1395,24 +1399,24 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>464.8</v>
+        <v>372.6</v>
       </c>
       <c r="S13" t="n">
-        <v>474.8</v>
+        <v>382.6</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
@@ -1422,33 +1426,29 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>464.8</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="D14" t="n">
-        <v>356.4</v>
-      </c>
+        <v>372.6</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>821.2</v>
+        <v>372.6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.22</v>
+        <v>0.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01</v>
+        <v>0.87</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>612.97</v>
+        <v>478.36</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -1459,90 +1459,88 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>en_movimiento</t>
+          <t>esperando_descenso</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>372.6</v>
+      </c>
+      <c r="S14" t="n">
+        <v>392.6</v>
+      </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>llegada_pasajero</t>
+          <t>llegada_ascensor</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>612.97</v>
+        <v>372.6</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>821.2</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>372.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.14</v>
+      </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="K15" t="n">
-        <v>392.79</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>1005.76</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="N15" t="inlineStr">
+        <v>478.36</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>baja</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>baja</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>en_movimiento</t>
+          <t>esperando_ascenso</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
-      </c>
-      <c r="R15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>372.6</v>
+      </c>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>402.6</v>
+      </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
@@ -1552,29 +1550,33 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>821.2</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+        <v>372.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D16" t="n">
+        <v>198</v>
+      </c>
       <c r="E16" t="n">
-        <v>821.2</v>
+        <v>570.6</v>
       </c>
       <c r="F16" t="n">
-        <v>0.84</v>
+        <v>0.21</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.93</v>
+        <v>0.41</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>1005.76</v>
+        <v>478.36</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -1585,63 +1587,65 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>esperando_descenso</t>
+          <t>en_movimiento</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>821.2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>846.2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>llegada_ascensor</t>
+          <t>llegada_pasajero</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>821.2</v>
+        <v>478.36</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>821.2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.78</v>
-      </c>
+        <v>570.6</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.8100000000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K17" t="n">
+        <v>124.65</v>
+      </c>
       <c r="L17" t="n">
-        <v>1005.76</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>603.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>baja</t>
@@ -1649,18 +1653,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>esperando_descenso</t>
+          <t>en_movimiento</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>821.2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>841.2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
@@ -1680,29 +1680,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>821.2</v>
+        <v>570.6</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>821.2</v>
+        <v>570.6</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>1005.76</v>
+        <v>603.01</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -1713,28 +1709,28 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>esperando_descenso</t>
+          <t>esperando_ascenso</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>821.2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>826.2</v>
-      </c>
-      <c r="T18" t="inlineStr"/>
+        <v>570.6</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>575.6</v>
+      </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -1744,29 +1740,29 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>821.2</v>
+        <v>570.6</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>821.2</v>
+        <v>570.6</v>
       </c>
       <c r="F19" t="n">
-        <v>0.21</v>
+        <v>0.74</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>1005.76</v>
+        <v>603.01</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -1781,24 +1777,24 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>821.2</v>
+        <v>570.6</v>
       </c>
       <c r="S19" t="n">
-        <v>826.2</v>
+        <v>590.6</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -1808,21 +1804,21 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>821.2</v>
+        <v>570.6</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>821.2</v>
+        <v>570.6</v>
       </c>
       <c r="F20" t="n">
-        <v>0.79</v>
+        <v>0.39</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1830,7 +1826,7 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>1005.76</v>
+        <v>603.01</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -1845,24 +1841,24 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>821.2</v>
+        <v>570.6</v>
       </c>
       <c r="S20" t="n">
-        <v>826.2</v>
+        <v>575.6</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21">
@@ -1872,25 +1868,33 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>821.2</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+        <v>570.6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="D21" t="n">
+        <v>291.6</v>
+      </c>
       <c r="E21" t="n">
-        <v>821.2</v>
+        <v>862.2</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>1005.76</v>
+        <v>603.01</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -1901,19 +1905,15 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>esperando_ascenso</t>
+          <t>en_movimiento</t>
         </is>
       </c>
       <c r="Q21" t="n">
         <v>5</v>
       </c>
-      <c r="R21" t="n">
-        <v>821.2</v>
-      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="n">
-        <v>826.2</v>
-      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
         <v>0</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2099,7 +2099,9 @@
           <t>semilla</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>2024</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/salida/simulacion.xlsx
+++ b/salida/simulacion.xlsx
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -864,13 +864,9 @@
         <v>372.6</v>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
@@ -920,13 +916,9 @@
         <v>372.6</v>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>5</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>0.71</v>
       </c>
